--- a/SAD/טבלת רכיבים.xlsx
+++ b/SAD/טבלת רכיבים.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25028"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Home\OneDrive - הקריה ללימודי הנדסה וטכנולוגיה\מסמכים\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dariel\Documents\GitHub\CyberWall\SAD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1BDFC890-C4AE-4C76-8E1B-6A21A5F3BA7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B6E640-EC5F-4A98-89CE-5820B85E75DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3348" yWindow="3348" windowWidth="17280" windowHeight="8964" xr2:uid="{5D1F83FE-506C-4710-B088-8F40CDCD1A99}"/>
+    <workbookView xWindow="1248" yWindow="2820" windowWidth="17280" windowHeight="8964" activeTab="1" xr2:uid="{5D1F83FE-506C-4710-B088-8F40CDCD1A99}"/>
   </bookViews>
   <sheets>
     <sheet name="App Serever Firebase" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="21">
   <si>
     <t>שם</t>
   </si>
@@ -86,7 +86,19 @@
     <t>אחסון נתונים</t>
   </si>
   <si>
-    <t>Report Mnager</t>
+    <t>Generate report</t>
+  </si>
+  <si>
+    <t>יצירת ושליחת דו''ח לשרת</t>
+  </si>
+  <si>
+    <t>מנהל דו''ת קריסת מערכת</t>
+  </si>
+  <si>
+    <t>Report Manager</t>
+  </si>
+  <si>
+    <t>Internal Storage Manager</t>
   </si>
 </sst>
 </file>
@@ -97,7 +109,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -216,7 +228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
@@ -230,20 +242,32 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -263,7 +287,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ערכת נושא Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -560,15 +584,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE9A2AAF-3566-47CD-982C-8CF3D418FD61}">
   <dimension ref="B4:F24"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.19921875" customWidth="1"/>
-    <col min="3" max="3" width="21.8984375" customWidth="1"/>
-    <col min="5" max="5" width="16.796875" customWidth="1"/>
-    <col min="6" max="6" width="18.59765625" customWidth="1"/>
+    <col min="2" max="2" width="10.21875" customWidth="1"/>
+    <col min="3" max="3" width="21.88671875" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" customWidth="1"/>
+    <col min="6" max="6" width="18.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B4" s="5" t="s">
         <v>0</v>
       </c>
@@ -581,7 +605,7 @@
       <c r="E4" s="1"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B5" s="8"/>
       <c r="C5" s="3"/>
       <c r="D5" s="4" t="s">
@@ -594,151 +618,161 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="B6" s="9" t="s">
+    <row r="6" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B6" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="12" t="s">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="10" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="2:6" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="B8" s="13" t="s">
+    <row r="8" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B8" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F8" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B9" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
@@ -751,19 +785,20 @@
     <mergeCell ref="C6:C7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2082887B-8870-4410-9316-388F5E700F68}">
   <dimension ref="B4:F24"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="16.796875" customWidth="1"/>
-    <col min="3" max="3" width="14.5" customWidth="1"/>
+    <col min="2" max="2" width="16.77734375" customWidth="1"/>
+    <col min="3" max="3" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B4" s="5" t="s">
         <v>0</v>
       </c>
@@ -776,7 +811,7 @@
       <c r="E4" s="1"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="4" t="s">
@@ -789,7 +824,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B6" s="6" t="s">
         <v>6</v>
       </c>
@@ -800,126 +835,138 @@
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
+    <row r="7" spans="2:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B7" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B8" s="16"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="10" t="s">
+        <v>10</v>
+      </c>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B9" s="17"/>
+      <c r="C9" s="14"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B10" s="7"/>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B10" s="6"/>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
@@ -927,6 +974,9 @@
       <c r="F24" s="7"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B8:B9"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/SAD/טבלת רכיבים.xlsx
+++ b/SAD/טבלת רכיבים.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dariel\Documents\GitHub\CyberWall\SAD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B6E640-EC5F-4A98-89CE-5820B85E75DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2EB47A1-766A-476D-9D97-B93AC18D6A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1248" yWindow="2820" windowWidth="17280" windowHeight="8964" activeTab="1" xr2:uid="{5D1F83FE-506C-4710-B088-8F40CDCD1A99}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="38">
   <si>
     <t>שם</t>
   </si>
@@ -62,9 +62,6 @@
     <t>הנתונים של האפליקציה על שרת האחסון</t>
   </si>
   <si>
-    <t xml:space="preserve">הנתונים אשר נשמרים בתוך האפליקציה </t>
-  </si>
-  <si>
     <t>Database Maneger</t>
   </si>
   <si>
@@ -99,19 +96,81 @@
   </si>
   <si>
     <t>Internal Storage Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הנתונים אשר נשמרים בתוך האפליקציה באופן זמני </t>
+  </si>
+  <si>
+    <t>Store data</t>
+  </si>
+  <si>
+    <t>נתוני שימוש האפליקציה</t>
+  </si>
+  <si>
+    <t>UserUI</t>
+  </si>
+  <si>
+    <t>הצגה למשתמש</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>מציג את הממשק הנדרש</t>
+  </si>
+  <si>
+    <t>Permission Manager</t>
+  </si>
+  <si>
+    <t>ניהול הרשאות האפליקציות</t>
+  </si>
+  <si>
+    <t>מאפשר למשתמש לבטל או לאשר הרשאה</t>
+  </si>
+  <si>
+    <t>Permission
+data</t>
+  </si>
+  <si>
+    <t>נתונים של מצב ההרשאות של כל האפליקציות</t>
+  </si>
+  <si>
+    <t>System languages manager</t>
+  </si>
+  <si>
+    <t>ניהול שפות המערכת</t>
+  </si>
+  <si>
+    <t>Languages</t>
+  </si>
+  <si>
+    <t>Permission</t>
+  </si>
+  <si>
+    <t>בחירת שפת מערכת</t>
+  </si>
+  <si>
+    <t>Packet capture manager</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="177"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -129,7 +188,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -224,20 +283,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -257,17 +326,53 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -606,7 +711,7 @@
       <c r="F4" s="2"/>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B5" s="8"/>
+      <c r="B5" s="7"/>
       <c r="C5" s="3"/>
       <c r="D5" s="4" t="s">
         <v>3</v>
@@ -619,165 +724,165 @@
       </c>
     </row>
     <row r="6" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="10" t="s">
+      <c r="E6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="F6" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="10" t="s">
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="10" t="s">
+      <c r="F7" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="10" t="s">
+    </row>
+    <row r="8" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B8" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B8" s="11" t="s">
+      <c r="F8" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B9" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B9" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -794,189 +899,253 @@
   <dimension ref="B4:F24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="16.77734375" customWidth="1"/>
-    <col min="3" max="3" width="14.44140625" customWidth="1"/>
+    <col min="2" max="2" width="18.77734375" customWidth="1"/>
+    <col min="3" max="3" width="22.88671875" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" customWidth="1"/>
+    <col min="6" max="6" width="21.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="4" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="2"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="27"/>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="4" t="s">
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="21" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B6" s="6" t="s">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B6" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-    </row>
-    <row r="7" spans="2:6" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="10" t="s">
+      <c r="C6" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B8" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="10" t="s">
+      <c r="C8" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B8" s="16"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B9" s="17"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B10" s="6"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
+      <c r="B9" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B10" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B11" s="18"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B12" s="19"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B13" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
+      <c r="B14" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B8:B9"/>
+  <mergeCells count="8">
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="B10:B12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/SAD/טבלת רכיבים.xlsx
+++ b/SAD/טבלת רכיבים.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dariel\Documents\GitHub\CyberWall\SAD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2EB47A1-766A-476D-9D97-B93AC18D6A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD3DAE8-355A-4146-9C83-B2055C29196A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1248" yWindow="2820" windowWidth="17280" windowHeight="8964" activeTab="1" xr2:uid="{5D1F83FE-506C-4710-B088-8F40CDCD1A99}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{5D1F83FE-506C-4710-B088-8F40CDCD1A99}"/>
   </bookViews>
   <sheets>
     <sheet name="App Serever Firebase" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="47">
   <si>
     <t>שם</t>
   </si>
@@ -93,9 +93,6 @@
   </si>
   <si>
     <t>Report Manager</t>
-  </si>
-  <si>
-    <t>Internal Storage Manager</t>
   </si>
   <si>
     <t xml:space="preserve">הנתונים אשר נשמרים בתוך האפליקציה באופן זמני </t>
@@ -144,13 +141,43 @@
     <t>Languages</t>
   </si>
   <si>
-    <t>Permission</t>
-  </si>
-  <si>
-    <t>בחירת שפת מערכת</t>
-  </si>
-  <si>
     <t>Packet capture manager</t>
+  </si>
+  <si>
+    <t>מסופק/נדרש</t>
+  </si>
+  <si>
+    <t>ניהול לכידת חבילות רשת</t>
+  </si>
+  <si>
+    <t>Packets</t>
+  </si>
+  <si>
+    <t>מנות רשת</t>
+  </si>
+  <si>
+    <t>Connections</t>
+  </si>
+  <si>
+    <t>מידע על חיבורי האפליקציות</t>
+  </si>
+  <si>
+    <t>ADVANCED MODE option manager</t>
+  </si>
+  <si>
+    <t>Permissions</t>
+  </si>
+  <si>
+    <t>ממשק לשימוש מתקדם</t>
+  </si>
+  <si>
+    <t>USER MODE option manager</t>
+  </si>
+  <si>
+    <t>שפת המערכת</t>
+  </si>
+  <si>
+    <t>ממשק לשימוש פשוט</t>
   </si>
 </sst>
 </file>
@@ -300,79 +327,73 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -688,7 +709,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE9A2AAF-3566-47CD-982C-8CF3D418FD61}">
-  <dimension ref="B4:F24"/>
+  <dimension ref="B4:F8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.21875" customWidth="1"/>
@@ -711,7 +732,7 @@
       <c r="F4" s="2"/>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B5" s="7"/>
+      <c r="B5" s="6"/>
       <c r="C5" s="3"/>
       <c r="D5" s="4" t="s">
         <v>3</v>
@@ -724,165 +745,51 @@
       </c>
     </row>
     <row r="6" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="9" t="s">
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="7" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="9" spans="2:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B9" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -896,254 +803,271 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2082887B-8870-4410-9316-388F5E700F68}">
-  <dimension ref="B4:F24"/>
+  <dimension ref="B4:F19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.77734375" customWidth="1"/>
     <col min="3" max="3" width="22.88671875" customWidth="1"/>
+    <col min="4" max="4" width="10.21875" customWidth="1"/>
     <col min="5" max="5" width="13.6640625" customWidth="1"/>
     <col min="6" max="6" width="21.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="4" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="25"/>
-      <c r="F4" s="27"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="22"/>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="22" t="s">
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="13" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="F6" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B7" s="23"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B9" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="9" t="s">
+      <c r="E9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B10" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B8" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="9" t="s">
+      <c r="E10" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B11" s="26"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B12" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B9" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B10" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B11" s="18"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B12" s="19"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B13" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="9" t="s">
+      <c r="E12" s="15" t="s">
         <v>33</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B13" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>36</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>36</v>
+      <c r="E13" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B15" s="12"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
+      <c r="F15" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
+      <c r="B18" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>45</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="13">
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="D4:F4"/>
-    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="B13:B14"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="C6:C7"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C13:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="300" r:id="rId1"/>
